--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20211.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20211.xlsx
@@ -551,25 +551,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="I3">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K3">
-        <v>50</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -586,25 +586,25 @@
         <v>43</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>53.49</v>
+        <v>58.14</v>
       </c>
       <c r="H4">
-        <v>46.51</v>
+        <v>41.86</v>
       </c>
       <c r="I4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K4">
-        <v>46.51</v>
+        <v>37.21</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -633,13 +633,13 @@
         <v>47.62</v>
       </c>
       <c r="I5">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>47.62</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -656,25 +656,25 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>70.97</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H6">
-        <v>29.03</v>
+        <v>12.9</v>
       </c>
       <c r="I6">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>29.03</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -691,25 +691,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>80.56</v>
+        <v>88.89</v>
       </c>
       <c r="H7">
-        <v>19.44</v>
+        <v>11.11</v>
       </c>
       <c r="I7">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>19.44</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -726,25 +726,25 @@
         <v>43</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>83.72</v>
+        <v>88.37</v>
       </c>
       <c r="H8">
-        <v>16.28</v>
+        <v>11.63</v>
       </c>
       <c r="I8">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>16.28</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -761,25 +761,25 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G9">
-        <v>74.42</v>
+        <v>88.37</v>
       </c>
       <c r="H9">
-        <v>25.58</v>
+        <v>11.63</v>
       </c>
       <c r="I9">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K9">
-        <v>25.58</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -831,25 +831,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>85.29000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="H11">
-        <v>14.71</v>
+        <v>5.88</v>
       </c>
       <c r="I11">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K11">
-        <v>14.71</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -866,25 +866,25 @@
         <v>40</v>
       </c>
       <c r="E12">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F12">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H12">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I12">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J12">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -950,22 +950,25 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>100</v>
+        <v>50</v>
+      </c>
+      <c r="I2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="K2">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -982,22 +985,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>34.09</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>65.91</v>
+      </c>
+      <c r="I3">
+        <v>8.9</v>
       </c>
       <c r="J3">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="K3">
-        <v>100</v>
+        <v>65.91</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1014,22 +1020,25 @@
         <v>43</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F4">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>37.21</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>62.79</v>
+      </c>
+      <c r="I4">
+        <v>9.1</v>
       </c>
       <c r="J4">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>62.79</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1046,22 +1055,25 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>47.62</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>52.38</v>
+      </c>
+      <c r="I5">
+        <v>9.5</v>
       </c>
       <c r="J5">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>52.38</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1078,22 +1090,25 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>19.35</v>
+      </c>
+      <c r="I6">
+        <v>6.8</v>
       </c>
       <c r="J6">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>19.35</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1110,22 +1125,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>77.78</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>22.22</v>
+      </c>
+      <c r="I7">
+        <v>8.4</v>
       </c>
       <c r="J7">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1142,22 +1160,25 @@
         <v>43</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F8">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>18.6</v>
+      </c>
+      <c r="I8">
+        <v>7.7</v>
       </c>
       <c r="J8">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1174,22 +1195,25 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F9">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>20.93</v>
+      </c>
+      <c r="I9">
+        <v>7.6</v>
       </c>
       <c r="J9">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1206,22 +1230,25 @@
         <v>24</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>9.199999999999999</v>
       </c>
       <c r="J10">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1238,22 +1265,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F11">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>14.71</v>
+      </c>
+      <c r="I11">
+        <v>7.3</v>
       </c>
       <c r="J11">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1270,22 +1300,25 @@
         <v>40</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F12">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I12">
+        <v>7.6</v>
       </c>
       <c r="J12">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1351,19 +1384,19 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>64.29000000000001</v>
+        <v>67.86</v>
       </c>
       <c r="H2">
-        <v>35.71</v>
+        <v>32.14</v>
       </c>
       <c r="I2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1386,25 +1419,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>59.09</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>40.91</v>
       </c>
       <c r="I3">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K3">
-        <v>50</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1421,25 +1454,25 @@
         <v>43</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>53.49</v>
+        <v>62.79</v>
       </c>
       <c r="H4">
-        <v>46.51</v>
+        <v>37.21</v>
       </c>
       <c r="I4">
         <v>8.4</v>
       </c>
       <c r="J4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K4">
-        <v>46.51</v>
+        <v>37.21</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1456,25 +1489,25 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>52.38</v>
+        <v>57.14</v>
       </c>
       <c r="H5">
-        <v>47.62</v>
+        <v>42.86</v>
       </c>
       <c r="I5">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>47.62</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1491,25 +1524,25 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>70.97</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H6">
-        <v>29.03</v>
+        <v>12.9</v>
       </c>
       <c r="I6">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>29.03</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1526,25 +1559,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>80.56</v>
+        <v>88.89</v>
       </c>
       <c r="H7">
-        <v>19.44</v>
+        <v>11.11</v>
       </c>
       <c r="I7">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>19.44</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1561,25 +1594,25 @@
         <v>43</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>83.72</v>
+        <v>88.37</v>
       </c>
       <c r="H8">
-        <v>16.28</v>
+        <v>11.63</v>
       </c>
       <c r="I8">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>16.28</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1596,25 +1629,25 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G9">
-        <v>74.42</v>
+        <v>88.37</v>
       </c>
       <c r="H9">
-        <v>25.58</v>
+        <v>11.63</v>
       </c>
       <c r="I9">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="J9">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K9">
-        <v>25.58</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1643,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>8.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1666,25 +1699,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>85.29000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="H11">
-        <v>14.71</v>
+        <v>5.88</v>
       </c>
       <c r="I11">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K11">
-        <v>14.71</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1701,25 +1734,25 @@
         <v>40</v>
       </c>
       <c r="E12">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F12">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H12">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I12">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J12">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20211.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20211.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
     <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="3er Parcial" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -109,6 +109,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -161,8 +165,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -463,42 +469,45 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -521,19 +530,19 @@
       <c r="F2">
         <v>10</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>64.29000000000001</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>35.71</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>7.8</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>3.57</v>
       </c>
     </row>
@@ -556,19 +565,19 @@
       <c r="F3">
         <v>20</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>54.55</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>45.45</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J3">
         <v>18</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>40.91</v>
       </c>
     </row>
@@ -591,19 +600,19 @@
       <c r="F4">
         <v>18</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>58.14</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>41.86</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>8</v>
       </c>
       <c r="J4">
         <v>16</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>37.21</v>
       </c>
     </row>
@@ -626,19 +635,19 @@
       <c r="F5">
         <v>10</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>52.38</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>47.62</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J5">
         <v>9</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>42.86</v>
       </c>
     </row>
@@ -661,19 +670,19 @@
       <c r="F6">
         <v>4</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>87.09999999999999</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>12.9</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>7.1</v>
       </c>
       <c r="J6">
         <v>4</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>12.9</v>
       </c>
     </row>
@@ -696,19 +705,19 @@
       <c r="F7">
         <v>4</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>88.89</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>11.11</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>8.33</v>
       </c>
     </row>
@@ -731,19 +740,19 @@
       <c r="F8">
         <v>5</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>88.37</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>11.63</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>8.1</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>9.300000000000001</v>
       </c>
     </row>
@@ -766,19 +775,19 @@
       <c r="F9">
         <v>5</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>88.37</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>11.63</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>7.6</v>
       </c>
       <c r="J9">
         <v>3</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>6.98</v>
       </c>
     </row>
@@ -801,19 +810,19 @@
       <c r="F10">
         <v>0</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>100</v>
       </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
         <v>8.800000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -836,19 +845,19 @@
       <c r="F11">
         <v>2</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>94.12</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>5.88</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>7.7</v>
       </c>
       <c r="J11">
         <v>2</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>5.88</v>
       </c>
     </row>
@@ -871,19 +880,19 @@
       <c r="F12">
         <v>10</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>75</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>25</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>7.4</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0</v>
       </c>
     </row>
@@ -897,42 +906,45 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -955,19 +967,19 @@
       <c r="F2">
         <v>14</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>50</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>50</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J2">
         <v>14</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>50</v>
       </c>
     </row>
@@ -990,19 +1002,19 @@
       <c r="F3">
         <v>29</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>34.09</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>65.91</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>8.9</v>
       </c>
       <c r="J3">
         <v>29</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>65.91</v>
       </c>
     </row>
@@ -1025,19 +1037,19 @@
       <c r="F4">
         <v>27</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>37.21</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>62.79</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>9.1</v>
       </c>
       <c r="J4">
         <v>27</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>62.79</v>
       </c>
     </row>
@@ -1060,19 +1072,19 @@
       <c r="F5">
         <v>11</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>47.62</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>52.38</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>9.5</v>
       </c>
       <c r="J5">
         <v>11</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>52.38</v>
       </c>
     </row>
@@ -1095,19 +1107,19 @@
       <c r="F6">
         <v>6</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>80.65000000000001</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>19.35</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>6.8</v>
       </c>
       <c r="J6">
         <v>6</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>19.35</v>
       </c>
     </row>
@@ -1130,19 +1142,19 @@
       <c r="F7">
         <v>8</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>77.78</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>22.22</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>8.4</v>
       </c>
       <c r="J7">
         <v>7</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>19.44</v>
       </c>
     </row>
@@ -1165,19 +1177,19 @@
       <c r="F8">
         <v>8</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>81.40000000000001</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>18.6</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>7.7</v>
       </c>
       <c r="J8">
         <v>7</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>16.28</v>
       </c>
     </row>
@@ -1200,19 +1212,19 @@
       <c r="F9">
         <v>9</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>79.06999999999999</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>20.93</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>7.6</v>
       </c>
       <c r="J9">
         <v>9</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>20.93</v>
       </c>
     </row>
@@ -1235,19 +1247,19 @@
       <c r="F10">
         <v>0</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>100</v>
       </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1270,19 +1282,19 @@
       <c r="F11">
         <v>5</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>85.29000000000001</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>14.71</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>7.3</v>
       </c>
       <c r="J11">
         <v>5</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>14.71</v>
       </c>
     </row>
@@ -1305,19 +1317,19 @@
       <c r="F12">
         <v>10</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>75</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>25</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>7.6</v>
       </c>
       <c r="J12">
         <v>10</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>25</v>
       </c>
     </row>
@@ -1331,42 +1343,45 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1389,19 +1404,19 @@
       <c r="F2">
         <v>9</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>67.86</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>32.14</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>8</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>3.57</v>
       </c>
     </row>
@@ -1424,19 +1439,19 @@
       <c r="F3">
         <v>18</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>59.09</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>40.91</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J3">
         <v>18</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>40.91</v>
       </c>
     </row>
@@ -1459,19 +1474,19 @@
       <c r="F4">
         <v>16</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>62.79</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>37.21</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>8.4</v>
       </c>
       <c r="J4">
         <v>16</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>37.21</v>
       </c>
     </row>
@@ -1494,19 +1509,19 @@
       <c r="F5">
         <v>9</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>57.14</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>42.86</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>8.800000000000001</v>
       </c>
       <c r="J5">
         <v>9</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>42.86</v>
       </c>
     </row>
@@ -1529,19 +1544,19 @@
       <c r="F6">
         <v>4</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>87.09999999999999</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>12.9</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>7.1</v>
       </c>
       <c r="J6">
         <v>4</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>12.9</v>
       </c>
     </row>
@@ -1564,19 +1579,19 @@
       <c r="F7">
         <v>4</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>88.89</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>11.11</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>8.4</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>8.33</v>
       </c>
     </row>
@@ -1599,19 +1614,19 @@
       <c r="F8">
         <v>5</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>88.37</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>11.63</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>8.1</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>9.300000000000001</v>
       </c>
     </row>
@@ -1634,19 +1649,19 @@
       <c r="F9">
         <v>5</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>88.37</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>11.63</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>7.7</v>
       </c>
       <c r="J9">
         <v>3</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>6.98</v>
       </c>
     </row>
@@ -1669,19 +1684,19 @@
       <c r="F10">
         <v>0</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>100</v>
       </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
         <v>9.300000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1704,19 +1719,19 @@
       <c r="F11">
         <v>2</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>94.12</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>5.88</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>7.7</v>
       </c>
       <c r="J11">
         <v>2</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>5.88</v>
       </c>
     </row>
@@ -1739,19 +1754,19 @@
       <c r="F12">
         <v>10</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>75</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>25</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>7.4</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20211.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20211.xlsx
@@ -110,7 +110,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20211.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20211.xlsx
@@ -962,25 +962,25 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1">
-        <v>50</v>
+        <v>53.57</v>
       </c>
       <c r="H2" s="1">
-        <v>50</v>
+        <v>46.43</v>
       </c>
       <c r="I2" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K2" s="1">
-        <v>50</v>
+        <v>46.43</v>
       </c>
     </row>
     <row r="3" spans="1:11">

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20211.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20211.xlsx
@@ -630,25 +630,25 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1">
-        <v>52.38</v>
+        <v>57.14</v>
       </c>
       <c r="H5" s="1">
-        <v>47.62</v>
+        <v>42.86</v>
       </c>
       <c r="I5" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K5" s="1">
-        <v>42.86</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1504,25 +1504,25 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="H5" s="1">
-        <v>42.86</v>
+        <v>38.1</v>
       </c>
       <c r="I5" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K5" s="1">
-        <v>42.86</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="6" spans="1:11">

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20211.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20211.xlsx
@@ -560,25 +560,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1">
-        <v>54.55</v>
+        <v>56.82</v>
       </c>
       <c r="H3" s="1">
-        <v>45.45</v>
+        <v>43.18</v>
       </c>
       <c r="I3" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K3" s="1">
-        <v>40.91</v>
+        <v>38.64</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -997,25 +997,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3" s="1">
-        <v>34.09</v>
+        <v>36.36</v>
       </c>
       <c r="H3" s="1">
-        <v>65.91</v>
+        <v>63.64</v>
       </c>
       <c r="I3" s="2">
         <v>8.9</v>
       </c>
       <c r="J3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K3" s="1">
-        <v>65.91</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1032,25 +1032,25 @@
         <v>43</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G4" s="1">
-        <v>37.21</v>
+        <v>44.19</v>
       </c>
       <c r="H4" s="1">
-        <v>62.79</v>
+        <v>55.81</v>
       </c>
       <c r="I4" s="2">
         <v>9.1</v>
       </c>
       <c r="J4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K4" s="1">
-        <v>62.79</v>
+        <v>55.81</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1067,25 +1067,25 @@
         <v>21</v>
       </c>
       <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5">
         <v>10</v>
       </c>
-      <c r="F5">
-        <v>11</v>
-      </c>
       <c r="G5" s="1">
+        <v>52.38</v>
+      </c>
+      <c r="H5" s="1">
         <v>47.62</v>
-      </c>
-      <c r="H5" s="1">
-        <v>52.38</v>
       </c>
       <c r="I5" s="2">
         <v>9.5</v>
       </c>
       <c r="J5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K5" s="1">
-        <v>52.38</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1222,10 +1222,10 @@
         <v>7.6</v>
       </c>
       <c r="J9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K9" s="1">
-        <v>20.93</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1434,25 +1434,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1">
-        <v>59.09</v>
+        <v>61.36</v>
       </c>
       <c r="H3" s="1">
-        <v>40.91</v>
+        <v>38.64</v>
       </c>
       <c r="I3" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K3" s="1">
-        <v>40.91</v>
+        <v>38.64</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1481,7 +1481,7 @@
         <v>37.21</v>
       </c>
       <c r="I4" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J4">
         <v>16</v>
@@ -1516,7 +1516,7 @@
         <v>38.1</v>
       </c>
       <c r="I5" s="2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
         <v>8</v>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20211.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20211.xlsx
@@ -525,25 +525,25 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1">
-        <v>64.29000000000001</v>
+        <v>67.86</v>
       </c>
       <c r="H2" s="1">
-        <v>35.71</v>
+        <v>32.14</v>
       </c>
       <c r="I2" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>3.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -560,25 +560,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1">
-        <v>56.82</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>43.18</v>
+        <v>18.18</v>
       </c>
       <c r="I3" s="2">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="J3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>38.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -595,25 +595,25 @@
         <v>43</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G4" s="1">
-        <v>58.14</v>
+        <v>69.77</v>
       </c>
       <c r="H4" s="1">
-        <v>41.86</v>
+        <v>30.23</v>
       </c>
       <c r="I4" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>37.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -642,13 +642,13 @@
         <v>42.86</v>
       </c>
       <c r="I5" s="2">
-        <v>8.1</v>
+        <v>6.9</v>
       </c>
       <c r="J5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>38.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -662,28 +662,28 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>87.09999999999999</v>
+        <v>90.63</v>
       </c>
       <c r="H6" s="1">
-        <v>12.9</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I6" s="2">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>12.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -712,13 +712,13 @@
         <v>11.11</v>
       </c>
       <c r="I7" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -747,13 +747,13 @@
         <v>11.63</v>
       </c>
       <c r="I8" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -782,13 +782,13 @@
         <v>11.63</v>
       </c>
       <c r="I9" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>6.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -840,25 +840,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H11" s="1">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="I11" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -962,25 +962,25 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>53.57</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>46.43</v>
+        <v>3.57</v>
       </c>
       <c r="I2" s="2">
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
       <c r="J2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>46.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -997,25 +997,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>36.36</v>
+        <v>86.36</v>
       </c>
       <c r="H3" s="1">
-        <v>63.64</v>
+        <v>13.64</v>
       </c>
       <c r="I3" s="2">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="J3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>63.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1032,25 +1032,25 @@
         <v>43</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
-        <v>44.19</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>55.81</v>
+        <v>23.26</v>
       </c>
       <c r="I4" s="2">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="J4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>55.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1067,25 +1067,25 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>52.38</v>
+        <v>61.9</v>
       </c>
       <c r="H5" s="1">
-        <v>47.62</v>
+        <v>38.1</v>
       </c>
       <c r="I5" s="2">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>47.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1099,28 +1099,28 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>80.65000000000001</v>
+        <v>90.63</v>
       </c>
       <c r="H6" s="1">
-        <v>19.35</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I6" s="2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>19.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1137,25 +1137,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1">
-        <v>77.78</v>
+        <v>83.33</v>
       </c>
       <c r="H7" s="1">
-        <v>22.22</v>
+        <v>16.67</v>
       </c>
       <c r="I7" s="2">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>19.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1172,25 +1172,25 @@
         <v>43</v>
       </c>
       <c r="E8">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>81.40000000000001</v>
+        <v>86.05</v>
       </c>
       <c r="H8" s="1">
-        <v>18.6</v>
+        <v>13.95</v>
       </c>
       <c r="I8" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>16.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1207,25 +1207,25 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1">
-        <v>79.06999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>20.93</v>
+        <v>18.6</v>
       </c>
       <c r="I9" s="2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J9">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>16.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1277,25 +1277,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>85.29000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="H11" s="1">
-        <v>14.71</v>
+        <v>2.94</v>
       </c>
       <c r="I11" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>14.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1324,13 +1324,13 @@
         <v>25</v>
       </c>
       <c r="I12" s="2">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1399,25 +1399,25 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>67.86</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>32.14</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>3.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1434,25 +1434,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1">
-        <v>61.36</v>
+        <v>79.55</v>
       </c>
       <c r="H3" s="1">
-        <v>38.64</v>
+        <v>20.45</v>
       </c>
       <c r="I3" s="2">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="J3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>38.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1469,25 +1469,25 @@
         <v>43</v>
       </c>
       <c r="E4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G4" s="1">
-        <v>62.79</v>
+        <v>69.77</v>
       </c>
       <c r="H4" s="1">
-        <v>37.21</v>
+        <v>30.23</v>
       </c>
       <c r="I4" s="2">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>37.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1516,13 +1516,13 @@
         <v>38.1</v>
       </c>
       <c r="I5" s="2">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="J5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>38.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1536,28 +1536,28 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6">
         <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>87.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="H6" s="1">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="I6" s="2">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>12.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1574,25 +1574,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>88.89</v>
+        <v>86.11</v>
       </c>
       <c r="H7" s="1">
-        <v>11.11</v>
+        <v>13.89</v>
       </c>
       <c r="I7" s="2">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1609,25 +1609,25 @@
         <v>43</v>
       </c>
       <c r="E8">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G8" s="1">
-        <v>88.37</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>11.63</v>
+        <v>18.6</v>
       </c>
       <c r="I8" s="2">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1644,25 +1644,25 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1">
-        <v>88.37</v>
+        <v>83.72</v>
       </c>
       <c r="H9" s="1">
-        <v>11.63</v>
+        <v>16.28</v>
       </c>
       <c r="I9" s="2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>6.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1691,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1714,25 +1714,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H11" s="1">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="I11" s="2">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1749,16 +1749,16 @@
         <v>40</v>
       </c>
       <c r="E12">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
         <v>7.4</v>
